--- a/raw data/Cycle_1.xlsx
+++ b/raw data/Cycle_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Documents\2_Academics_Career\3_INTERNSHIP\7_Research\Orthopedic DVT audit submission\Orthopedic_Thromboprophylaxis_Audit\raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE953EC-1713-4714-B1EB-68C8F0B3F550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9BA253-5406-4196-BC65-818C0BE0449C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{8261274D-0555-4A2A-A23D-FAD3C46842B4}"/>
   </bookViews>
@@ -1356,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C143995-17F5-41ED-AC6E-0D308D904CC9}">
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27.4140625" bestFit="1" customWidth="1"/>
@@ -7419,6 +7419,12 @@
         <v>8</v>
       </c>
     </row>
+    <row r="102" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R102">
+        <f>COUNTIF(R1:R101, "Hip")</f>
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
